--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-procedures.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-procedures.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-procedures.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-procedures.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="120">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -383,16 +383,6 @@
   </si>
   <si>
     <t>Entrée Acte</t>
-  </si>
-  <si>
-    <t>fr-lm-procedures.entry.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-references-externes
-</t>
-  </si>
-  <si>
-    <t>Entrée Références externes</t>
   </si>
 </sst>
 </file>
@@ -694,7 +684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.64453125" customWidth="true" bestFit="true"/>
@@ -707,7 +697,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2044,106 +2034,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
